--- a/ConfigWorkspace/Data/tile_state.xlsx
+++ b/ConfigWorkspace/Data/tile_state.xlsx
@@ -1275,15 +1275,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="11" max="11" width="28.5545454545455" customWidth="1"/>
-    <col min="12" max="12" width="17.9272727272727" customWidth="1"/>
-    <col min="13" max="13" width="18.9" customWidth="1"/>
+    <col min="10" max="10" width="28.5545454545455" customWidth="1"/>
+    <col min="11" max="11" width="17.9272727272727" customWidth="1"/>
+    <col min="12" max="12" width="18.9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1294,40 +1294,34 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="F1" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="K1" s="5" t="s">
+        <v>11</v>
+      </c>
       <c r="L1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1338,40 +1332,34 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F2" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="J2" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="K2" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -1384,7 +1372,7 @@
       <c r="D3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F3" s="2" t="s">
@@ -1396,26 +1384,20 @@
       <c r="H3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="5" t="s">
         <v>27</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -1426,40 +1408,34 @@
         <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="E4" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="F4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>37</v>
       </c>
+      <c r="J4" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="K4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="L4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="N4" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
         <v>42</v>
@@ -1467,11 +1443,13 @@
       <c r="C5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1">
+      <c r="D5" s="1">
         <v>10</v>
       </c>
-      <c r="F5" s="2" t="b">
+      <c r="E5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
         <v>0</v>
       </c>
       <c r="G5" s="2">
@@ -1480,26 +1458,20 @@
       <c r="H5" s="2">
         <v>0</v>
       </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K5" s="2" t="s">
+      <c r="I5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="1">
+      <c r="K5" s="1">
         <v>1</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N5" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>47</v>
@@ -1507,11 +1479,13 @@
       <c r="C6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1">
+      <c r="D6" s="1">
         <v>10</v>
       </c>
-      <c r="F6" s="2" t="b">
+      <c r="E6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
         <v>0</v>
       </c>
       <c r="G6" s="2">
@@ -1520,24 +1494,18 @@
       <c r="H6" s="2">
         <v>0</v>
       </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1" t="s">
+      <c r="I6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="N6" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
         <v>49</v>
@@ -1545,11 +1513,13 @@
       <c r="C7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1">
+      <c r="D7" s="1">
         <v>8</v>
       </c>
-      <c r="F7" s="2" t="b">
+      <c r="E7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
         <v>0</v>
       </c>
       <c r="G7" s="2">
@@ -1558,26 +1528,20 @@
       <c r="H7" s="2">
         <v>0</v>
       </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K7" s="2" t="s">
+      <c r="I7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="K7" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="L7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="M7" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="N7" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
         <v>53</v>
@@ -1585,11 +1549,13 @@
       <c r="C8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1">
+      <c r="D8" s="1">
         <v>15</v>
       </c>
-      <c r="F8" s="2" t="b">
+      <c r="E8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
         <v>0</v>
       </c>
       <c r="G8" s="2">
@@ -1598,24 +1564,18 @@
       <c r="H8" s="2">
         <v>0</v>
       </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1" t="s">
+      <c r="I8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="N8" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
         <v>55</v>
@@ -1623,11 +1583,13 @@
       <c r="C9" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1">
+      <c r="D9" s="1">
         <v>20</v>
       </c>
-      <c r="F9" s="2" t="b">
+      <c r="E9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
         <v>0</v>
       </c>
       <c r="G9" s="2">
@@ -1636,26 +1598,20 @@
       <c r="H9" s="2">
         <v>0</v>
       </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K9" s="2" t="s">
+      <c r="I9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L9" s="1">
+      <c r="K9" s="1">
         <v>1</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="N9" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
         <v>58</v>
@@ -1663,11 +1619,13 @@
       <c r="C10" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1">
+      <c r="D10" s="1">
         <v>20</v>
       </c>
-      <c r="F10" s="2" t="b">
+      <c r="E10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
         <v>0</v>
       </c>
       <c r="G10" s="2">
@@ -1676,26 +1634,20 @@
       <c r="H10" s="2">
         <v>0</v>
       </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K10" s="2" t="s">
+      <c r="I10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="1">
+      <c r="K10" s="1">
         <v>1</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="N10" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
         <v>59</v>
@@ -1703,41 +1655,35 @@
       <c r="C11" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="1" t="b">
+      <c r="D11" s="1">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K11" s="1">
         <v>1</v>
       </c>
-      <c r="E11" s="1">
-        <v>3</v>
-      </c>
-      <c r="F11" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L11" s="1">
-        <v>1</v>
-      </c>
-      <c r="M11" s="1" t="s">
+      <c r="L11" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="N11" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
         <v>62</v>
@@ -1745,13 +1691,13 @@
       <c r="C12" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1">
+      <c r="D12" s="1">
         <v>3</v>
       </c>
-      <c r="F12" s="2" t="b">
+      <c r="E12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
         <v>0</v>
       </c>
       <c r="G12" s="2">
@@ -1760,26 +1706,20 @@
       <c r="H12" s="2">
         <v>0</v>
       </c>
-      <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K12" s="2" t="s">
+      <c r="I12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>63</v>
       </c>
+      <c r="K12" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="L12" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="M12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="N12" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
         <v>65</v>
@@ -1787,11 +1727,13 @@
       <c r="C13" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1">
+      <c r="D13" s="1">
         <v>15</v>
       </c>
-      <c r="F13" s="2" t="b">
+      <c r="E13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
         <v>0</v>
       </c>
       <c r="G13" s="2">
@@ -1800,26 +1742,20 @@
       <c r="H13" s="2">
         <v>0</v>
       </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K13" s="2" t="s">
+      <c r="I13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>66</v>
       </c>
+      <c r="K13" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="L13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="M13" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="N13" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
         <v>68</v>
@@ -1827,11 +1763,13 @@
       <c r="C14" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="b">
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
         <v>0</v>
       </c>
       <c r="G14" s="2">
@@ -1840,24 +1778,18 @@
       <c r="H14" s="2">
         <v>0</v>
       </c>
-      <c r="I14" s="2">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1" t="s">
+      <c r="I14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="N14" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
         <v>70</v>
@@ -1865,11 +1797,13 @@
       <c r="C15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1">
+      <c r="D15" s="1">
         <v>3</v>
       </c>
-      <c r="F15" s="2" t="b">
+      <c r="E15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
         <v>0</v>
       </c>
       <c r="G15" s="2">
@@ -1878,26 +1812,20 @@
       <c r="H15" s="2">
         <v>0</v>
       </c>
-      <c r="I15" s="2">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K15" s="2" t="s">
+      <c r="I15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="L15" s="1">
+      <c r="K15" s="1">
         <v>2</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="N15" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
         <v>72</v>
@@ -1905,11 +1833,13 @@
       <c r="C16" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1">
+      <c r="D16" s="1">
         <v>5</v>
       </c>
-      <c r="F16" s="2" t="b">
+      <c r="E16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
         <v>0</v>
       </c>
       <c r="G16" s="2">
@@ -1918,24 +1848,18 @@
       <c r="H16" s="2">
         <v>0</v>
       </c>
-      <c r="I16" s="2">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="I16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
         <v>73</v>
@@ -1943,37 +1867,33 @@
       <c r="C17" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1">
+      <c r="D17" s="1">
         <v>-1</v>
       </c>
-      <c r="F17" s="2" t="b">
+      <c r="E17" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
       <c r="G17" s="2">
         <v>0</v>
       </c>
       <c r="H17" s="2">
         <v>0</v>
       </c>
-      <c r="I17" s="2">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6" t="s">
+      <c r="I17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="N17" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
         <v>75</v>
@@ -1981,37 +1901,33 @@
       <c r="C18" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1">
+      <c r="D18" s="1">
         <v>-1</v>
       </c>
-      <c r="F18" s="2" t="b">
+      <c r="E18" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
       <c r="G18" s="2">
         <v>0</v>
       </c>
       <c r="H18" s="2">
         <v>0</v>
       </c>
-      <c r="I18" s="2">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="s">
+      <c r="I18" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="K18" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6" t="s">
+      <c r="J18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="N18" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="4"/>
       <c r="B19" s="1" t="s">
         <v>77</v>
@@ -2019,37 +1935,33 @@
       <c r="C19" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1">
+      <c r="D19" s="1">
         <v>-1</v>
       </c>
-      <c r="F19" s="2" t="b">
+      <c r="E19" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="F19" s="2">
+        <v>4</v>
+      </c>
       <c r="G19" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H19" s="2">
         <v>0</v>
       </c>
-      <c r="I19" s="2">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L19" s="7"/>
-      <c r="M19" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="I19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K19" s="7"/>
+      <c r="L19" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="4"/>
       <c r="B20" s="1" t="s">
         <v>78</v>
@@ -2057,37 +1969,33 @@
       <c r="C20" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1">
+      <c r="D20" s="1">
         <v>-1</v>
       </c>
-      <c r="F20" s="2" t="b">
+      <c r="E20" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="F20" s="2">
+        <v>-4</v>
+      </c>
       <c r="G20" s="2">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="H20" s="2">
-        <v>2</v>
-      </c>
-      <c r="I20" s="2">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L20" s="7"/>
-      <c r="M20" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="4"/>
       <c r="B21" s="1" t="s">
         <v>79</v>
@@ -2095,37 +2003,33 @@
       <c r="C21" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1">
+      <c r="D21" s="1">
         <v>-1</v>
       </c>
-      <c r="F21" s="2" t="b">
+      <c r="E21" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="F21" s="2">
+        <v>1</v>
+      </c>
       <c r="G21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="2">
-        <v>0</v>
-      </c>
-      <c r="I21" s="2">
         <v>2</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L21" s="7"/>
-      <c r="M21" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="I21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K21" s="7"/>
+      <c r="L21" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="4"/>
       <c r="B22" s="1" t="s">
         <v>80</v>
@@ -2133,39 +2037,35 @@
       <c r="C22" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1">
+      <c r="D22" s="1">
         <v>-1</v>
       </c>
-      <c r="F22" s="2" t="b">
+      <c r="E22" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
       <c r="G22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K22" s="1">
         <v>1</v>
       </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K22" s="2" t="s">
+      <c r="L22" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="L22" s="1">
-        <v>1</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
         <v>81</v>
@@ -2173,34 +2073,30 @@
       <c r="C23" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2">
+      <c r="D23" s="2">
         <v>-1</v>
       </c>
-      <c r="F23" s="2" t="b">
+      <c r="E23" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="F23" s="2">
+        <v>0</v>
+      </c>
       <c r="G23" s="2">
         <v>0</v>
       </c>
       <c r="H23" s="2">
         <v>0</v>
       </c>
-      <c r="I23" s="2">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>46</v>
+      <c r="I23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/ConfigWorkspace/Data/tile_state.xlsx
+++ b/ConfigWorkspace/Data/tile_state.xlsx
@@ -1616,7 +1616,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>

--- a/ConfigWorkspace/Data/tile_state.xlsx
+++ b/ConfigWorkspace/Data/tile_state.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CBABD44-C64B-4E71-AF8E-3768293455AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F79E8F-0E37-4AC4-81BF-8DFD8839C8F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3945" yWindow="3810" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -90,9 +90,6 @@
     <t>移速倍率(1=不减速)</t>
   </si>
   <si>
-    <t>每秒伤害(0=无)</t>
-  </si>
-  <si>
     <t>物理阻挡墙体</t>
   </si>
   <si>
@@ -151,13 +148,46 @@
   </si>
   <si>
     <t>霜冻冰刺</t>
+  </si>
+  <si>
+    <t>touch_stun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>f</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>loat</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>麻痹时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每秒伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,6 +198,14 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -192,8 +230,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -496,490 +540,560 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="4" max="4" width="16.875" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="17" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H4" t="s">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B5" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5">
+      <c r="C5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="1">
         <v>-1</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H5" t="s">
+      <c r="C6" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B6">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D6" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D6">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="1">
         <v>-1</v>
       </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B7">
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="1">
+        <v>10</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="1">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="1">
         <v>15</v>
       </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7">
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="1">
+        <v>8</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="1">
+        <v>3</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="1">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="1">
         <v>-1</v>
       </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8">
-        <v>10</v>
-      </c>
-      <c r="E8">
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1">
         <v>0.5</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B9">
-        <v>3</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9">
-        <v>8</v>
-      </c>
-      <c r="E9">
-        <v>1.2</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B10">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10">
-        <v>-1</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B11">
-        <v>18</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11">
-        <v>-1</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B12">
-        <v>17</v>
-      </c>
-      <c r="C12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12">
-        <v>-1</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B13">
-        <v>19</v>
-      </c>
-      <c r="C13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13">
-        <v>-1</v>
-      </c>
-      <c r="E13">
-        <v>0.7</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14">
-        <v>15</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B15">
-        <v>5</v>
-      </c>
-      <c r="C15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15">
-        <v>8</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15" t="s">
-        <v>25</v>
-      </c>
-      <c r="H15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B16">
-        <v>8</v>
-      </c>
-      <c r="C16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16">
-        <v>3</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B17">
-        <v>20</v>
-      </c>
-      <c r="C17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17">
-        <v>3</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B18">
-        <v>21</v>
-      </c>
-      <c r="C18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18">
-        <v>3</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="F18">
-        <v>2</v>
-      </c>
-      <c r="G18" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B19">
-        <v>22</v>
-      </c>
-      <c r="C19" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19">
-        <v>-1</v>
-      </c>
-      <c r="E19">
-        <v>0.4</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" t="s">
-        <v>25</v>
-      </c>
-      <c r="H19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B20">
-        <v>23</v>
-      </c>
-      <c r="C20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20">
-        <v>-1</v>
-      </c>
-      <c r="E20">
-        <v>0.5</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20" t="s">
-        <v>25</v>
-      </c>
-      <c r="H20" t="s">
-        <v>25</v>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{1F599E73-E934-458C-85EC-D3257A64A782}">
+      <formula1>"空地,基础水,基础土,普通泥浆,稀泥,基础火池,基础电源,基础冰面,基础植物区,陶砖,结冰,蒸汽,导电区,燎原火海,带电荆棘,霜冻冰刺"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ConfigWorkspace/Data/tile_state.xlsx
+++ b/ConfigWorkspace/Data/tile_state.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F79E8F-0E37-4AC4-81BF-8DFD8839C8F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC6788A-9418-4ADF-925D-10CB7A83527D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11025" yWindow="3690" windowWidth="19785" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -180,6 +180,13 @@
   </si>
   <si>
     <t>每秒伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础花</t>
+  </si>
+  <si>
+    <t>基础花</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -540,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1086,11 +1093,37 @@
         <v>24</v>
       </c>
     </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{1F599E73-E934-458C-85EC-D3257A64A782}">
-      <formula1>"空地,基础水,基础土,普通泥浆,稀泥,基础火池,基础电源,基础冰面,基础植物区,陶砖,结冰,蒸汽,导电区,燎原火海,带电荆棘,霜冻冰刺"</formula1>
+      <formula1>"空地,基础水,基础土,普通泥浆,稀泥,基础火池,基础电源,基础冰面,基础植物区,陶砖,结冰,蒸汽,导电区,燎原火海,带电荆棘,霜冻冰刺,基础花"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ConfigWorkspace/Data/tile_state.xlsx
+++ b/ConfigWorkspace/Data/tile_state.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC6788A-9418-4ADF-925D-10CB7A83527D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBDA118-F764-436C-A3B0-7A5DC1A646E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11025" yWindow="3690" windowWidth="19785" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6800" yWindow="1800" windowWidth="15080" windowHeight="11670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -548,20 +548,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.90625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="17" style="1" customWidth="1"/>
     <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.90625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="14" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -590,7 +590,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -619,7 +619,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -648,7 +648,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -677,7 +677,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>23</v>
       </c>
@@ -703,7 +703,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>25</v>
       </c>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -729,7 +729,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>27</v>
       </c>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -755,7 +755,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>28</v>
       </c>
@@ -781,7 +781,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>29</v>
       </c>
@@ -807,7 +807,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>30</v>
       </c>
@@ -833,7 +833,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>31</v>
       </c>
@@ -859,7 +859,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>32</v>
       </c>
@@ -885,7 +885,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>33</v>
       </c>
@@ -911,7 +911,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>34</v>
       </c>
@@ -919,7 +919,7 @@
         <v>34</v>
       </c>
       <c r="D14" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
@@ -937,7 +937,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>35</v>
       </c>
@@ -963,7 +963,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>36</v>
       </c>
@@ -989,7 +989,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>37</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>39</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>39</v>
       </c>
       <c r="D19" s="1">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -1058,7 +1058,7 @@
         <v>0.4</v>
       </c>
       <c r="G19" s="1">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>24</v>
@@ -1067,7 +1067,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>40</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>40</v>
       </c>
       <c r="D20" s="1">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -1093,7 +1093,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>46</v>
       </c>

--- a/ConfigWorkspace/Data/tile_state.xlsx
+++ b/ConfigWorkspace/Data/tile_state.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityHub\Unity Project\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBDA118-F764-436C-A3B0-7A5DC1A646E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16AC5ABF-733E-4A43-801B-D224F887B1A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6800" yWindow="1800" windowWidth="15080" windowHeight="11670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="336" yWindow="3096" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -548,16 +548,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.90625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="17" style="1" customWidth="1"/>
     <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="14" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -855,8 +855,8 @@
       <c r="H11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>24</v>
+      <c r="I11" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">

--- a/ConfigWorkspace/Data/tile_state.xlsx
+++ b/ConfigWorkspace/Data/tile_state.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityHub\Unity Project\deepseaoil\ConfigWorkspace\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16AC5ABF-733E-4A43-801B-D224F887B1A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C286891-534A-487A-A8F7-C68A7E78FFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="336" yWindow="3096" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2985" yWindow="2970" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -548,20 +548,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="17" style="1" customWidth="1"/>
     <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="14" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -590,7 +590,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -619,7 +619,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -648,7 +648,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -677,7 +677,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>23</v>
       </c>
@@ -703,7 +703,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B6" s="1" t="s">
         <v>25</v>
       </c>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -729,7 +729,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>27</v>
       </c>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -755,7 +755,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>28</v>
       </c>
@@ -769,7 +769,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -781,7 +781,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B9" s="1" t="s">
         <v>29</v>
       </c>
@@ -807,7 +807,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B10" s="1" t="s">
         <v>30</v>
       </c>
@@ -833,7 +833,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
         <v>31</v>
       </c>
@@ -859,7 +859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B12" s="1" t="s">
         <v>32</v>
       </c>
@@ -885,7 +885,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B13" s="1" t="s">
         <v>33</v>
       </c>
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -911,7 +911,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B14" s="1" t="s">
         <v>34</v>
       </c>
@@ -937,7 +937,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B15" s="1" t="s">
         <v>35</v>
       </c>
@@ -963,7 +963,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>36</v>
       </c>
@@ -989,7 +989,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>37</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B19" s="1" t="s">
         <v>39</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="1">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G19" s="1">
         <v>3</v>
@@ -1067,7 +1067,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B20" s="1" t="s">
         <v>40</v>
       </c>
@@ -1081,7 +1081,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -1093,7 +1093,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B21" s="1" t="s">
         <v>46</v>
       </c>

--- a/ConfigWorkspace/Data/tile_state.xlsx
+++ b/ConfigWorkspace/Data/tile_state.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC6788A-9418-4ADF-925D-10CB7A83527D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C286891-534A-487A-A8F7-C68A7E78FFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11025" yWindow="3690" windowWidth="19785" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2985" yWindow="2970" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -769,7 +769,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -855,8 +855,8 @@
       <c r="H11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>24</v>
+      <c r="I11" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.15">
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -919,7 +919,7 @@
         <v>34</v>
       </c>
       <c r="D14" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
@@ -1049,16 +1049,16 @@
         <v>39</v>
       </c>
       <c r="D19" s="1">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
       </c>
       <c r="F19" s="1">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G19" s="1">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>24</v>
@@ -1075,13 +1075,13 @@
         <v>40</v>
       </c>
       <c r="D20" s="1">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
       </c>
       <c r="F20" s="1">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>

--- a/ConfigWorkspace/Data/tile_state.xlsx
+++ b/ConfigWorkspace/Data/tile_state.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C286891-534A-487A-A8F7-C68A7E78FFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A2C95D-6914-4458-B452-0CA2FAA298B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2985" yWindow="2970" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3105" yWindow="3300" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1049,7 +1049,7 @@
         <v>39</v>
       </c>
       <c r="D19" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>

--- a/ConfigWorkspace/Data/tile_state.xlsx
+++ b/ConfigWorkspace/Data/tile_state.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A2C95D-6914-4458-B452-0CA2FAA298B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACB589D-FD1A-4E9C-80D4-7826E78DC639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3105" yWindow="3300" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -919,7 +919,7 @@
         <v>34</v>
       </c>
       <c r="D14" s="1">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
@@ -1049,7 +1049,7 @@
         <v>39</v>
       </c>
       <c r="D19" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>

--- a/ConfigWorkspace/Data/tile_state.xlsx
+++ b/ConfigWorkspace/Data/tile_state.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C286891-534A-487A-A8F7-C68A7E78FFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACB589D-FD1A-4E9C-80D4-7826E78DC639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2985" yWindow="2970" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3105" yWindow="3300" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -919,7 +919,7 @@
         <v>34</v>
       </c>
       <c r="D14" s="1">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
@@ -1049,7 +1049,7 @@
         <v>39</v>
       </c>
       <c r="D19" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>

--- a/ConfigWorkspace/Data/tile_state.xlsx
+++ b/ConfigWorkspace/Data/tile_state.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityHub\Unity Project\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACB589D-FD1A-4E9C-80D4-7826E78DC639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83179406-BC48-41FA-A9C4-9C1DEC49366F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3105" yWindow="3300" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3168" yWindow="1812" windowWidth="17280" windowHeight="11448" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -39,10 +39,13 @@
     <t>duration</t>
   </si>
   <si>
+    <t>dot_damage</t>
+  </si>
+  <si>
     <t>slow_rate</t>
   </si>
   <si>
-    <t>dot_damage</t>
+    <t>touch_stun</t>
   </si>
   <si>
     <t>is_obstacle</t>
@@ -51,6 +54,9 @@
     <t>is_conductor</t>
   </si>
   <si>
+    <t>priority</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -69,6 +75,9 @@
     <t>bool</t>
   </si>
   <si>
+    <t>int!#range=[0,99]</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -87,9 +96,15 @@
     <t>存活秒数(-1=永久)</t>
   </si>
   <si>
+    <t>每秒伤害</t>
+  </si>
+  <si>
     <t>移速倍率(1=不减速)</t>
   </si>
   <si>
+    <t>麻痹时间</t>
+  </si>
+  <si>
     <t>物理阻挡墙体</t>
   </si>
   <si>
@@ -150,44 +165,11 @@
     <t>霜冻冰刺</t>
   </si>
   <si>
-    <t>touch_stun</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>f</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>loat</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>麻痹时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每秒伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>基础花</t>
   </si>
   <si>
-    <t>基础花</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>覆盖优先级</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -203,16 +185,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -242,7 +224,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -548,20 +530,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="17" style="1" customWidth="1"/>
     <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="9" style="1"/>
+    <col min="9" max="9" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -575,114 +558,126 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+        <v>15</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+        <v>18</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+        <v>27</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D5" s="1">
         <v>-1</v>
@@ -697,18 +692,21 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+        <v>29</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1">
         <v>-1</v>
@@ -723,18 +721,21 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+        <v>31</v>
+      </c>
+      <c r="J6" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1">
         <v>-1</v>
@@ -749,18 +750,21 @@
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+        <v>31</v>
+      </c>
+      <c r="J7" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D8" s="1">
         <v>10</v>
@@ -775,18 +779,21 @@
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+        <v>31</v>
+      </c>
+      <c r="J8" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1">
         <v>8</v>
@@ -801,18 +808,21 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+        <v>31</v>
+      </c>
+      <c r="J9" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D10" s="1">
         <v>-1</v>
@@ -827,18 +837,21 @@
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+        <v>29</v>
+      </c>
+      <c r="J10" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D11" s="1">
         <v>-1</v>
@@ -853,18 +866,21 @@
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I11" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J11" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D12" s="1">
         <v>-1</v>
@@ -879,18 +895,21 @@
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
+        <v>29</v>
+      </c>
+      <c r="J12" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D13" s="1">
         <v>-1</v>
@@ -905,18 +924,21 @@
         <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+        <v>29</v>
+      </c>
+      <c r="J13" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D14" s="1">
         <v>15</v>
@@ -931,18 +953,21 @@
         <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+        <v>29</v>
+      </c>
+      <c r="J14" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D15" s="1">
         <v>8</v>
@@ -957,18 +982,21 @@
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+        <v>29</v>
+      </c>
+      <c r="J15" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D16" s="1">
         <v>3</v>
@@ -983,18 +1011,21 @@
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.15">
+        <v>29</v>
+      </c>
+      <c r="J16" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -1009,18 +1040,21 @@
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
+        <v>31</v>
+      </c>
+      <c r="J17" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D18" s="1">
         <v>3</v>
@@ -1035,24 +1069,27 @@
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.15">
+        <v>29</v>
+      </c>
+      <c r="J18" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D19" s="1">
         <v>15</v>
       </c>
       <c r="E19" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="1">
         <v>0.5</v>
@@ -1061,44 +1098,50 @@
         <v>3</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.15">
+        <v>29</v>
+      </c>
+      <c r="J19" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D20" s="1">
         <v>10</v>
       </c>
       <c r="E20" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="1">
         <v>0.6</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.15">
+        <v>29</v>
+      </c>
+      <c r="J20" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D21" s="1">
         <v>-1</v>
@@ -1118,11 +1161,14 @@
       <c r="I21" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="J21" s="1">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{1F599E73-E934-458C-85EC-D3257A64A782}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"空地,基础水,基础土,普通泥浆,稀泥,基础火池,基础电源,基础冰面,基础植物区,陶砖,结冰,蒸汽,导电区,燎原火海,带电荆棘,霜冻冰刺,基础花"</formula1>
     </dataValidation>
   </dataValidations>

--- a/ConfigWorkspace/Data/tile_state.xlsx
+++ b/ConfigWorkspace/Data/tile_state.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityHub\Unity Project\deepseaoil\ConfigWorkspace\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83179406-BC48-41FA-A9C4-9C1DEC49366F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11DEF64-7C06-4A3B-AE73-664DEA523BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3168" yWindow="1812" windowWidth="17280" windowHeight="11448" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11790" yWindow="2820" windowWidth="18345" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -195,6 +195,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -530,21 +531,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="17" style="1" customWidth="1"/>
     <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.25" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="14" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -576,7 +577,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -608,7 +609,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -640,7 +641,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
@@ -672,7 +673,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>28</v>
       </c>
@@ -701,7 +702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="1" t="s">
         <v>30</v>
       </c>
@@ -730,7 +731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>32</v>
       </c>
@@ -759,7 +760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>33</v>
       </c>
@@ -788,7 +789,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B9" s="1" t="s">
         <v>34</v>
       </c>
@@ -817,7 +818,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="1" t="s">
         <v>35</v>
       </c>
@@ -846,7 +847,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
         <v>36</v>
       </c>
@@ -875,7 +876,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="1" t="s">
         <v>37</v>
       </c>
@@ -904,7 +905,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1" t="s">
         <v>38</v>
       </c>
@@ -933,7 +934,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="1" t="s">
         <v>39</v>
       </c>
@@ -962,7 +963,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="1" t="s">
         <v>40</v>
       </c>
@@ -991,7 +992,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>41</v>
       </c>
@@ -1020,7 +1021,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>42</v>
       </c>
@@ -1049,7 +1050,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B18" s="1" t="s">
         <v>43</v>
       </c>
@@ -1078,7 +1079,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B19" s="1" t="s">
         <v>44</v>
       </c>
@@ -1086,28 +1087,28 @@
         <v>44</v>
       </c>
       <c r="D19" s="1">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E19" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19" s="1">
         <v>0.5</v>
       </c>
       <c r="G19" s="1">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>29</v>
+      <c r="I19" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="J19" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B20" s="1" t="s">
         <v>45</v>
       </c>
@@ -1136,7 +1137,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B21" s="1" t="s">
         <v>46</v>
       </c>

--- a/ConfigWorkspace/Data/tile_state.xlsx
+++ b/ConfigWorkspace/Data/tile_state.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11DEF64-7C06-4A3B-AE73-664DEA523BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66131429-1DF2-4B7F-ADF8-3921D72C4FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11790" yWindow="2820" windowWidth="18345" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6660" yWindow="4470" windowWidth="21555" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -931,7 +931,7 @@
         <v>29</v>
       </c>
       <c r="J13" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.15">

--- a/ConfigWorkspace/Data/tile_state.xlsx
+++ b/ConfigWorkspace/Data/tile_state.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66131429-1DF2-4B7F-ADF8-3921D72C4FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F41E67-21C2-445F-9030-07F30EB39AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6660" yWindow="4470" windowWidth="21555" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11535" yWindow="5400" windowWidth="21555" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1105,7 +1105,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.15">
@@ -1134,7 +1134,7 @@
         <v>29</v>
       </c>
       <c r="J20" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.15">

--- a/ConfigWorkspace/Data/tile_state.xlsx
+++ b/ConfigWorkspace/Data/tile_state.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11DEF64-7C06-4A3B-AE73-664DEA523BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F41E67-21C2-445F-9030-07F30EB39AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11790" yWindow="2820" windowWidth="18345" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11535" yWindow="5400" windowWidth="21555" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -931,7 +931,7 @@
         <v>29</v>
       </c>
       <c r="J13" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.15">
@@ -1105,7 +1105,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.15">
@@ -1134,7 +1134,7 @@
         <v>29</v>
       </c>
       <c r="J20" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.15">
